--- a/research/psps_reports/round5/audit_sheet_rechecked.xlsx
+++ b/research/psps_reports/round5/audit_sheet_rechecked.xlsx
@@ -68,7 +68,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -87,6 +87,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -858,7 +859,7 @@
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>zero</t>
+          <t>not_stated</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
@@ -868,7 +869,7 @@
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>PSPS protacol not initiated so not applicable</t>
+          <t>Report says Section 7 is not applicable because PSPS protocols weren't initiated; rules code that as not_stated.</t>
         </is>
       </c>
     </row>
@@ -1017,17 +1018,19 @@
           <t>de-energized; circuit; time</t>
         </is>
       </c>
-      <c r="I9" s="6" t="n">
-        <v>44081.60486111111</v>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>2020-09-07 04:25</t>
+        </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>Pueblo 2103's 9/7/2020 4:25 (p56) is about 10 hours before every other 9/7 circuit (next: Kanaka 1101 at 14:31, p54). Its Napa neighbor Pueblo 2102 is 9/8/2020 4:07 (p56), so the date is likely an error for 9/8. Treated as an error; the first de-energization is Kanaka 1101 at 14:31.</t>
+          <t>Pueblo 2103 at 9/7 4:25 (p56) is about 10 hours before any other 9/7 circuit and may be a report error, but nothing in the report says so; following the rule.</t>
         </is>
       </c>
     </row>
@@ -1119,15 +1122,19 @@
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>2020/09-25 02:46</t>
+          <t>2019-09-23 17:06</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="n"/>
+          <t>7;15</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>Two-phase event; first de-energization Sept 23 at 17:06 (p7). The p4 table's 2020/09-25 02:46 is Bravo phase only, with a year typo.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="86.40000000000001" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -1736,12 +1743,12 @@
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7;8</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>UNSURE: No customers de energized</t>
+          <t>No customers de-energized (p7; Table 1 shows 0 de-energized, p8).</t>
         </is>
       </c>
     </row>
@@ -2200,17 +2207,17 @@
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>not_stated</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5;10;38</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>UNSURE: No customers de energized</t>
+          <t>UNSURE: no advance notices were sent; shutoff notices went only to the 86 customers de-energized (p38). Leaning no over not_stated.</t>
         </is>
       </c>
     </row>
